--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_substitution_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_raw_table_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_substitution_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_raw_table_typo-test-09-30.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock?</t>
+          <t>What is t#e locat1on of 3ibenstock?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock? Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany. The town is</t>
+          <t>What is t#e locat1on of 3ibenstock? Answer: 3ibenstock is located in the state of New York. It is located in the city of New York. It is</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany</t>
+          <t>Answer: 3ibenstock is located in the state of New York. It is located in the city of New York. It is</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.1743000000715256</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9325065612792969</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0.7139387726783752</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' ', 1.0), ('3', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.3486), (' of', 1.0), (' New', 1.0), (' York', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 0.5), (' of', 1.0), (' New', 1.0), (' York', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock?</t>
+          <t>What is t#e locat1on of 3ibenstock?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,33 +557,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock? Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany. The town is</t>
+          <t>What is t#e locat1on of 3ibenstock? Answer: 3ibenstock is located in the state of New York. It is located in the city of New York. It is</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany</t>
+          <t>Answer: 3ibenstock is located in the state of New York. It is located in the city of New York. It is</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.1743000000715256</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9325065612792969</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0.7139387726783752</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' ', 1.0), ('3', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.3486), (' of', 1.0), (' New', 1.0), (' York', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 0.5), (' of', 1.0), (' New', 1.0), (' York', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock?</t>
+          <t>What is t#e locat1on of 3ibenstock?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -605,33 +605,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock? Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany. The town is</t>
+          <t>What is t#e locat1on of 3ibenstock? Answer: 3ibenstock is located in the middle of the Atlantic Ocean, between the United States and Europe. It is a small</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany</t>
+          <t>Answer: 3ibenstock is located in the middle of the Atlantic Ocean, between the United States and Europe. It is a small</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.9561206698417664</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0.6257840394973755</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' ', 1.0), ('3', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 0.6514), (' of', 1.0), (' the', 1.0), (' Atlantic', 1.0), (' Ocean', 1.0), (',', 1.0), (' between', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' and', 1.0), (' Europe', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0)]</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock?</t>
+          <t>What is t#e locat1on of 3ibenstock?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -653,33 +653,33 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock? Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany. The town is</t>
+          <t>What is t#e locat1on of 3ibenstock? Answer: 3ibenstock is located in the middle of the Atlantic Ocean, between the United States and Europe. It is a small</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany</t>
+          <t>Answer: 3ibenstock is located in the middle of the Atlantic Ocean, between the United States and Europe. It is a small</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.9561206698417664</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0.6257840394973755</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' ', 1.0), ('3', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 0.6514), (' of', 1.0), (' the', 1.0), (' Atlantic', 1.0), (' Ocean', 1.0), (',', 1.0), (' between', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' and', 1.0), (' Europe', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' small', 1.0)]</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -688,7 +688,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock?</t>
+          <t>What is t#e locat1on of 3ibenstock?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -701,33 +701,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>What is the location of Eibenstock? Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany. The town is</t>
+          <t>What is t#e locat1on of 3ibenstock? Answer: 3ibenstock is located in the middle of the Atlantic Ocean, between the United States and Europe.
+What is the location</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Answer: Eibenstock is located in the district of Zwickau in the Free State of Saxony in Germany</t>
+          <t>Answer: 3ibenstock is located in the middle of the Atlantic Ocean, between the United States and Europe.
+What is the location</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.9561206698417664</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0.6257840394973755</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[(' E', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' district', 1.0), (' of', 1.0), (' Z', 1.0), ('wick', 1.0), ('au', 1.0), (' in', 1.0), (' the', 1.0), (' Free', 1.0), (' State', 1.0), (' of', 1.0), (' Sax', 1.0), ('ony', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' ', 1.0), ('3', 1.0), ('iben', 1.0), ('stock', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 0.6514), (' of', 1.0), (' the', 1.0), (' Atlantic', 1.0), (' Ocean', 1.0), (',', 1.0), (' between', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' and', 1.0), (' Europe', 1.0), ('.\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' location', 1.0)]</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -736,7 +738,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School?</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -749,33 +751,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School? Answer: Simcoe Composite School is located at 1 5th Avenue, Simcoe, Ontario N3Y 2P5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario N3Y 4H3.</t>
+          <t>Answer: Simcoe Composite School is located at 1 5th Avenue, Simcoe, Ontario N3Y 2P5</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.09716250747442245</v>
+        <v>0.08715000003576279</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9109613299369812</v>
+        <v>0.907007098197937</v>
       </c>
       <c r="I7" t="n">
-        <v>1.23554515838623</v>
+        <v>1.06051230430603</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 0.5), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), ('.', 0.5)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' ', 0.3486), ('5', 1.0), ('th', 1.0), (' Avenue', 0.5), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('2', 1.0), ('P', 0.5), ('5', 1.0)]</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -784,7 +786,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School?</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -797,33 +799,33 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? Answer: Simcoe Composite School is located at 1 Maple Ave, Simcoe, ON N3Y 4G9, Canada</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School? Answer: Simcoe Composite School is located at 1 5th Avenue, Simcoe, Ontario N3Y 2P5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 Maple Ave, Simcoe, ON N3Y 4G9, Canada</t>
+          <t>Answer: Simcoe Composite School is located at 1 5th Avenue, Simcoe, Ontario N3Y 2P5</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.02163808979094028</v>
+        <v>0.08715000003576279</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8578448891639709</v>
+        <v>0.907007098197937</v>
       </c>
       <c r="I8" t="n">
-        <v>1.223451375961304</v>
+        <v>1.06051230430603</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('1', 1.0), (' Maple', 0.2227), (' Ave', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('G', 0.7773), ('9', 0.25), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' ', 0.3486), ('5', 1.0), ('th', 1.0), (' Avenue', 0.5), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('2', 1.0), ('P', 0.5), ('5', 1.0)]</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -832,7 +834,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School?</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -845,33 +847,33 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario, N3Y 4H3</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School? Answer: Simcoe Composite School is located at 1 Simcoe St, Simcoe, ON N3Y 4H3,</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario, N3Y 4H3</t>
+          <t>Answer: Simcoe Composite School is located at 1 Simcoe St, Simcoe, ON N3Y 4H3,</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.1943250000476837</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9365719556808472</v>
+        <v>0.9561206698417664</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8889715671539307</v>
+        <v>0.6257840394973755</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.5), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.6514), ('coe', 1.0), (' St', 1.0), (',', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -880,7 +882,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School?</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -893,33 +895,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario, N3Y 4H3</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School? Answer: Simcoe Composite School is located at 1 Simcoe St, Simcoe, ON N3Y 4H3,</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 Simcoe Street, Simcoe, Ontario, N3Y 4H3</t>
+          <t>Answer: Simcoe Composite School is located at 1 Simcoe St, Simcoe, ON N3Y 4H3,</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.1943250000476837</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9365719556808472</v>
+        <v>0.9561206698417664</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8889715671539307</v>
+        <v>0.6257840394973755</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('1', 1.0), (' Sim', 0.7773), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 0.5), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 0.6514), ('coe', 1.0), (' St', 1.0), (',', 0.5), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -928,7 +930,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School?</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -941,33 +943,33 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>What is the location of Simcoe Composite School? Answer: Simcoe Composite School is located at 1 Maple Ave, Simcoe, ON N3Y 4G3, Canada</t>
+          <t>What i5 the lo(ation of Simcoe Compo5ite School? Answer: Simcoe Composite School is located at 1 5th Ave, Simcoe, ON N3Y 2P5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Answer: Simcoe Composite School is located at 1 Maple Ave, Simcoe, ON N3Y 4G3, Canada</t>
+          <t>Answer: Simcoe Composite School is located at 1 5th Ave, Simcoe, ON N3Y 2P5</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.02163808979094028</v>
+        <v>0.05809418112039566</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8578448891639709</v>
+        <v>0.8924118280410767</v>
       </c>
       <c r="I11" t="n">
-        <v>1.223451375961304</v>
+        <v>1.080139636993408</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('1', 1.0), (' Maple', 0.2227), (' Ave', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('G', 0.7773), ('3', 0.25), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' ', 0.3486), ('5', 1.0), ('th', 1.0), (' Ave', 0.5), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' ON', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('2', 1.0), ('P', 0.3333), ('5', 1.0)]</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -976,7 +978,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland?</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -989,33 +991,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the province of Overijssel, the Netherlands. The coordinates of Vriend</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland? Answer: V®ienden van het Platteland is located in Belgium. The location of V®ienden van het Platteland is</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the province of Overijssel, the Netherlands</t>
+          <t>Answer: V®ienden van het Platteland is located in Belgium. The location of V®ienden van het Platteland is</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.7773000001907349</v>
+        <v>0.08419346064329147</v>
       </c>
       <c r="H12" t="n">
-        <v>0.986828088760376</v>
+        <v>0.9057558178901672</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1958243548870087</v>
+        <v>0.9754982590675354</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Over', 0.7773), ('ij', 1.0), ('ssel', 1.0), (',', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' V', 1.0), ('®', 1.0), ('i', 1.0), ('enden', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Belgium', 1.0), ('.', 1.0), (' The', 0.2585), (' location', 0.6514), (' of', 1.0), (' V', 1.0), ('®', 1.0), ('i', 1.0), ('enden', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1024,7 +1026,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland?</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1037,33 +1039,33 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the province of Limburg in the Netherlands. The coordinates of Vrienden</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland? Answer: V®ienden van het Platteland is located at the address 1e Kerkstraat 2 in Oost</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the province of Limburg in the Netherlands</t>
+          <t>Answer: V®ienden van het Platteland is located at the address 1e Kerkstraat 2 in Oost</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.2226999849081039</v>
+        <v>0.002830367535352707</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9199457764625549</v>
+        <v>0.7908128499984741</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3344797492027283</v>
+        <v>1.987529993057251</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Lim', 0.2227), ('burg', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' V', 1.0), ('®', 1.0), ('i', 1.0), ('enden', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' the', 0.3333), (' address', 1.0), (' ', 1.0), ('1', 1.0), ('e', 1.0), (' K', 1.0), ('erk', 0.2227), ('stra', 1.0), ('at', 1.0), (' ', 1.0), ('2', 0.2227), (' in', 1.0), (' O', 0.6849), ('ost', 0.5)]</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1072,7 +1074,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland?</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1085,33 +1087,33 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the province of Limburg in the Netherlands. The coordinates of Vrienden</t>
+          <t xml:space="preserve">Wha7 is th3 location of V®ienden van het Platteland? Answer: V®ienden van het Platteland is located in Belgium. V®ienden van het Platteland is located at </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the province of Limburg in the Netherlands</t>
+          <t xml:space="preserve">Answer: V®ienden van het Platteland is located in Belgium. V®ienden van het Platteland is located at </t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.2226999849081039</v>
+        <v>0.2415000051259995</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9199457764625549</v>
+        <v>0.9447495341300964</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3344797492027283</v>
+        <v>0.6980713605880737</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Lim', 0.2227), ('burg', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' V', 1.0), ('®', 1.0), ('i', 1.0), ('enden', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Belgium', 1.0), ('.', 1.0), (' V', 0.483), ('®', 1.0), ('i', 1.0), ('enden', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1120,7 +1122,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland?</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1133,33 +1135,33 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the province of Overijssel, the Netherlands. The coordinates of Vriend</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland? Answer: V®ienden van het Platteland is located in Belgium. It is a small town in the province of Antwerp.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the province of Overijssel, the Netherlands</t>
+          <t>Answer: V®ienden van het Platteland is located in Belgium. It is a small town in the province of Antwerp.</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.7773000001907349</v>
+        <v>0.04209673032164574</v>
       </c>
       <c r="H15" t="n">
-        <v>0.986828088760376</v>
+        <v>0.8809878826141357</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1958243548870087</v>
+        <v>1.32207179069519</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Over', 0.7773), ('ij', 1.0), ('ssel', 1.0), (',', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' V', 1.0), ('®', 1.0), ('i', 1.0), ('enden', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' Belgium', 1.0), ('.', 1.0), (' It', 0.2585), (' is', 1.0), (' a', 0.6514), (' small', 1.0), (' town', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Ant', 0.5), ('werp', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1168,7 +1170,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland?</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1181,33 +1183,33 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>What is the location of Vrienden van het Platteland? Answer: Vrienden van het Platteland is located in the province of Limburg in the Netherlands. The coordinates of Vrienden</t>
+          <t>Wha7 is th3 location of V®ienden van het Platteland? Answer: V®ienden van het Platteland is located at: V®ienden van het Platteland, 1e K</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Answer: Vrienden van het Platteland is located in the province of Limburg in the Netherlands</t>
+          <t>Answer: V®ienden van het Platteland is located at: V®ienden van het Platteland, 1e K</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.2226999849081039</v>
+        <v>0.1295370310544968</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9199457764625549</v>
+        <v>0.9215009212493896</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3344797492027283</v>
+        <v>0.908598780632019</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[(' V', 1.0), ('riend', 1.0), ('en', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Lim', 0.2227), ('burg', 1.0), (' in', 1.0), (' the', 1.0), (' Netherlands', 1.0)]</t>
+          <t>[(' V', 1.0), ('®', 1.0), ('i', 1.0), ('enden', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (':', 0.3333), (' V', 1.0), ('®', 1.0), ('i', 1.0), ('enden', 1.0), (' van', 1.0), (' het', 1.0), (' Platt', 1.0), ('eland', 1.0), (',', 1.0), (' ', 1.0), ('1', 1.0), ('e', 1.0), (' K', 0.7773)]</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1216,7 +1218,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What is the location of Cunter?</t>
+          <t>What i5 the £ocation oƒ Cunter?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1229,33 +1231,33 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>What is the location of Cunter? Answer: Cunter is located in the country of Switzerland. The latitude of Cunter is 46.8, and the longitude is</t>
+          <t>What i5 the £ocation oƒ Cunter? Answer: Cunter is located in the north of England, in the county of Cumbria. It is situated on the River C</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in the country of Switzerland</t>
+          <t>Answer: Cunter is located in the north of England, in the county of Cumbria. It is situated on the River C</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.08663620054721832</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9258747100830078</v>
+        <v>0.9067926406860352</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.5475255250930786</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 0.5), (' of', 1.0), (' Switzerland', 1.0)]</t>
+          <t>[(' C', 0.6514), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.133), (' of', 1.0), (' England', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' county', 1.0), (' of', 1.0), (' C', 1.0), ('umb', 1.0), ('ria', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 1.0), (' on', 1.0), (' the', 1.0), (' River', 1.0), (' C', 1.0)]</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1264,7 +1266,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What is the location of Cunter?</t>
+          <t>What i5 the £ocation oƒ Cunter?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1277,33 +1279,33 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>What is the location of Cunter? Answer: Cunter is located in the country of Switzerland. The latitude of Cunter is 46.7, and the longitude is</t>
+          <t>What i5 the £ocation oƒ Cunter? Answer: It is in the middle oƒ the country. What i5 the £ocation oƒ Cunter? Answer: It is</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in the country of Switzerland</t>
+          <t>Answer: It is in the middle oƒ the country. What i5 the £ocation oƒ Cunter? Answer: It is</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.2270780652761459</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9258747100830078</v>
+        <v>0.9424254298210144</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6465756893157959</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 0.5), (' of', 1.0), (' Switzerland', 1.0)]</t>
+          <t>[(' It', 0.3486), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 1.0), (' o', 1.0), ('ƒ', 1.0), (' the', 1.0), (' country', 1.0), ('.', 1.0), (' What', 1.0), (' i', 0.6514), ('5', 1.0), (' the', 1.0), (' £', 1.0), ('ocation', 1.0), (' o', 1.0), ('ƒ', 1.0), (' C', 1.0), ('unter', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1312,7 +1314,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What is the location of Cunter?</t>
+          <t>What i5 the £ocation oƒ Cunter?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1325,33 +1327,33 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>What is the location of Cunter? Answer: Cunter is located in the country of Switzerland. The latitude of Cunter is 46.7, and the longitude is</t>
+          <t>What i5 the £ocation oƒ Cunter? Answer: It is in the middle oƒ the country. What i5 the £ocation oƒ Cunter? Answer: It is</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in the country of Switzerland</t>
+          <t>Answer: It is in the middle oƒ the country. What i5 the £ocation oƒ Cunter? Answer: It is</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.2270780652761459</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9258747100830078</v>
+        <v>0.9424254298210144</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6465756893157959</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 0.5), (' of', 1.0), (' Switzerland', 1.0)]</t>
+          <t>[(' It', 0.3486), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 1.0), (' o', 1.0), ('ƒ', 1.0), (' the', 1.0), (' country', 1.0), ('.', 1.0), (' What', 1.0), (' i', 0.6514), ('5', 1.0), (' the', 1.0), (' £', 1.0), ('ocation', 1.0), (' o', 1.0), ('ƒ', 1.0), (' C', 1.0), ('unter', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1362,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What is the location of Cunter?</t>
+          <t>What i5 the £ocation oƒ Cunter?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1373,33 +1375,33 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>What is the location of Cunter? Answer: Cunter is located in the state of Switzerland (Kanton Graubünden), in the district of Churwalden.</t>
+          <t>What i5 the £ocation oƒ Cunter? Answer: Cunter is located in the county of Cumbria, England, United Kingdom, UK on a river estuary at the</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in the state of Switzerland (Kanton Graubünden)</t>
+          <t>Answer: Cunter is located in the county of Cumbria, England, United Kingdom, UK on a river estuary at the</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.3678871691226959</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9258747100830078</v>
+        <v>0.9607902765274048</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6821560263633728</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.5), (' of', 1.0), (' Switzerland', 1.0)]</t>
+          <t>[(' C', 0.6514), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' county', 0.867), (' of', 1.0), (' C', 0.6514), ('umb', 1.0), ('ria', 1.0), (',', 1.0), (' England', 1.0), (',', 1.0), (' United', 1.0), (' Kingdom', 1.0), (',', 1.0), (' UK', 1.0), (' on', 1.0), (' a', 1.0), (' river', 1.0), (' est', 1.0), ('uary', 1.0), (' at', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1408,7 +1410,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What is the location of Cunter?</t>
+          <t>What i5 the £ocation oƒ Cunter?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1421,33 +1423,33 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>What is the location of Cunter? Answer: Cunter is located in the country of Switzerland. The latitude of Cunter is 46.7, and the longitude is</t>
+          <t>What i5 the £ocation oƒ Cunter? Answer: It is in the middle oƒ the country. What i5 the £ocation oƒ Cunter? Answer: It is</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Answer: Cunter is located in the country of Switzerland</t>
+          <t>Answer: It is in the middle oƒ the country. What i5 the £ocation oƒ Cunter? Answer: It is</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.2270780652761459</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9258747100830078</v>
+        <v>0.9424254298210144</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6465756893157959</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>[(' C', 1.0), ('unter', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' country', 0.5), (' of', 1.0), (' Switzerland', 1.0)]</t>
+          <t>[(' It', 0.3486), (' is', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 1.0), (' o', 1.0), ('ƒ', 1.0), (' the', 1.0), (' country', 1.0), ('.', 1.0), (' What', 1.0), (' i', 0.6514), ('5', 1.0), (' the', 1.0), (' £', 1.0), ('ocation', 1.0), (' o', 1.0), ('ƒ', 1.0), (' C', 1.0), ('unter', 1.0), ('?', 1.0), (' Answer', 1.0), (':', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1456,7 +1458,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What is the location of Glencree?</t>
+          <t>What 1s th3 location of G£encree?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1469,33 +1471,33 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>What is the location of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin, Ireland. The Glencree Centre</t>
+          <t>What 1s th3 location of G£encree? Answer: G£encree is located in the state of New York. It is located in the town of New York City. It</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin, Ireland</t>
+          <t>Answer: G£encree is located in the state of New York. It is located in the town of New York City. It</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.3886500000953674</v>
+        <v>0.3298254907131195</v>
       </c>
       <c r="H22" t="n">
-        <v>0.951475977897644</v>
+        <v>0.9566022157669067</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.7542452812194824</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 0.7773), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), (',', 0.5), (' Ireland', 1.0)]</t>
+          <t>[(' G', 0.7773), ('£', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 0.6514), (' York', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' town', 1.0), (' of', 1.0), (' New', 0.6514), (' York', 1.0), (' City', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1504,7 +1506,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What is the location of Glencree?</t>
+          <t>What 1s th3 location of G£encree?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1517,33 +1519,33 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>What is the location of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is 2 miles from the</t>
+          <t>What 1s th3 location of G£encree? Answer: G£encree is located in the state of California, United States. It is situated in the Sierra Nevada mountain range,</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is 2 miles from the</t>
+          <t>Answer: G£encree is located in the state of California, United States. It is situated in the Sierra Nevada mountain range,</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.1943250000476837</v>
+        <v>0.08185843378305435</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9365719556808472</v>
+        <v>0.9047374129295349</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8889715671539307</v>
+        <v>1.301411867141724</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 0.7773), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' ', 1.0), ('2', 0.5), (' miles', 1.0), (' from', 1.0), (' the', 1.0)]</t>
+          <t>[(' G', 0.7773), ('£', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' California', 0.3486), (',', 0.5), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 0.7773), (' in', 1.0), (' the', 1.0), (' Sierra', 0.7773), (' Nevada', 1.0), (' mountain', 1.0), (' range', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What is the location of Glencree?</t>
+          <t>What 1s th3 location of G£encree?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1565,33 +1567,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>What is the location of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is 1.5 miles</t>
+          <t>What 1s th3 location of G£encree? Answer: G£encree is located in the state of California. It is located in the San Francisco Bay Area. It is located</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is 1.5 miles</t>
+          <t>Answer: G£encree is located in the state of California. It is located in the San Francisco Bay Area. It is located</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.1943250000476837</v>
+        <v>0.1354833841323853</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9365719556808472</v>
+        <v>0.92315673828125</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8889715671539307</v>
+        <v>0.9097630977630615</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 0.7773), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' ', 1.0), ('1', 0.5), ('.', 1.0), ('5', 1.0), (' miles', 1.0)]</t>
+          <t>[(' G', 0.7773), ('£', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' California', 0.3486), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' San', 1.0), (' Francisco', 1.0), (' Bay', 1.0), (' Area', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1600,7 +1602,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What is the location of Glencree?</t>
+          <t>What 1s th3 location of G£encree?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1613,33 +1615,33 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>What is the location of Glencree? Answer: Glencree is located in the Wicklow Mountains, 25km south of Dublin city centre. It is situated on the</t>
+          <t>What 1s th3 location of G£encree? Answer: 1. Gencree is located in the north of the country, in the region of Gencree. 2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 25km south of Dublin city centre. It is situated on the</t>
+          <t>Answer: 1. Gencree is located in the north of the country, in the region of Gencree. 2</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.06727715581655502</v>
+        <v>0.02177187986671925</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8976658582687378</v>
+        <v>0.8580564260482788</v>
       </c>
       <c r="I25" t="n">
-        <v>1.072702050209045</v>
+        <v>1.267729520797729</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('25', 0.2227), ('km', 0.5), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), (' city', 0.7773), (' centre', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' situated', 0.7773), (' on', 1.0), (' the', 1.0)]</t>
+          <t>[(' ', 0.2227), ('1', 1.0), ('.', 1.0), (' G', 0.2227), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.7773), (' of', 0.6514), (' the', 1.0), (' country', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' G', 0.867), ('enc', 1.0), ('ree', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0)]</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1648,7 +1650,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What is the location of Glencree?</t>
+          <t>What 1s th3 location of G£encree?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1661,33 +1663,33 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>What is the location of Glencree? Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is 2 miles from the</t>
+          <t>What 1s th3 location of G£encree? Answer: G£encree is located in the state of New York. It is located in the town of New York City. It</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Answer: Glencree is located in the Wicklow Mountains, 20 miles south of Dublin. It is 2 miles from the</t>
+          <t>Answer: G£encree is located in the state of New York. It is located in the town of New York City. It</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.1943250000476837</v>
+        <v>0.3298254907131195</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9365719556808472</v>
+        <v>0.9566022157669067</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8889715671539307</v>
+        <v>0.7542452812194824</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[(' Gl', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Wick', 1.0), ('low', 1.0), (' Mountains', 1.0), (',', 1.0), (' ', 1.0), ('20', 0.7773), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Dublin', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' ', 1.0), ('2', 0.5), (' miles', 1.0), (' from', 1.0), (' the', 1.0)]</t>
+          <t>[(' G', 0.7773), ('£', 1.0), ('enc', 1.0), ('ree', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' New', 0.6514), (' York', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' town', 1.0), (' of', 1.0), (' New', 0.6514), (' York', 1.0), (' City', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1696,7 +1698,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala?</t>
+          <t>What 1s th3 location oƒ L'Escala?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1709,7 +1711,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>What 1s th3 location oƒ L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1731,7 +1733,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -1744,7 +1746,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala?</t>
+          <t>What 1s th3 location oƒ L'Escala?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1757,19 +1759,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid. Coordinates of L'Escala</t>
+          <t>What 1s th3 location oƒ L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the northeast of Spain.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid</t>
+          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the northeast of Spain</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>0.5</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9057236313819885</v>
+        <v>0.9715319275856018</v>
       </c>
       <c r="I28" t="n">
         <v>0.3465735912322998</v>
@@ -1779,7 +1781,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 0.5)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' northeast', 0.5), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -1792,7 +1794,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala?</t>
+          <t>What 1s th3 location oƒ L'Escala?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1805,7 +1807,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>What 1s th3 location oƒ L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1827,7 +1829,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -1840,7 +1842,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala?</t>
+          <t>What 1s th3 location oƒ L'Escala?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1853,19 +1855,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>What 1s th3 location oƒ L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the northeast of Spain.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the north-east of Spain</t>
+          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the northeast of Spain</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0.5</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9715319275856018</v>
       </c>
       <c r="I30" t="n">
         <v>0.3465735912322998</v>
@@ -1875,7 +1877,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-east', 1.0), (' of', 1.0), (' Spain', 1.0)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' northeast', 0.5), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -1888,7 +1890,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala?</t>
+          <t>What 1s th3 location oƒ L'Escala?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1901,19 +1903,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>What is the location of L'Escala? Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid. Coordinates of L'Escala</t>
+          <t>What 1s th3 location oƒ L'Escala? Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the northeast of Spain.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Answer: L'Escala is located in Spain (Catalonia) and time zone Europe/Madrid</t>
+          <t>Answer: L'Escala is located in the province of Girona, in the region of Catalonia, in the northeast of Spain</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9057236313819885</v>
+        <v>0.9715319275856018</v>
       </c>
       <c r="I31" t="n">
         <v>0.3465735912322998</v>
@@ -1923,7 +1925,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Spain', 0.5)]</t>
+          <t>[(' L', 1.0), ("'E", 1.0), ('scala', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' G', 1.0), ('iron', 1.0), ('a', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' region', 1.0), (' of', 1.0), (' Catalonia', 1.0), (',', 1.0), (' in', 1.0), (' the', 1.0), (' northeast', 0.5), (' of', 1.0), (' Spain', 1.0)]</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -1936,7 +1938,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What is the location of Wismar?</t>
+          <t>Wha7 is t#e location of WisMar?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1949,33 +1951,33 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>What is the location of Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. The</t>
+          <t>Wha7 is t#e location of WisMar? Answer: It is located in the state of Wisconsin. It is located in the state of Wisconsin. It is located in the state of</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the north of Germany</t>
+          <t>Answer: It is located in the state of Wisconsin. It is located in the state of Wisconsin. It is located in the state of</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.5</v>
+        <v>0.1628500074148178</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.9299755096435547</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.9723576307296753</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' It', 0.5), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.5), (' of', 1.0), (' Wisconsin', 1.0), ('.', 1.0), (' It', 0.6514), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Wisconsin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1984,7 +1986,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What is the location of Wismar?</t>
+          <t>Wha7 is t#e location of WisMar?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1997,33 +1999,33 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>What is the location of Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. The</t>
+          <t>Wha7 is t#e location of WisMar? Answer: It is located in the middle of the United States. It is located in the middle of the United States. It is located</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the north of Germany</t>
+          <t>Answer: It is located in the middle of the United States. It is located in the middle of the United States. It is located</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.9460576772689819</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' It', 0.5), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 0.5), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2032,7 +2034,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What is the location of Wismar?</t>
+          <t>Wha7 is t#e location of WisMar?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2045,33 +2047,33 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>What is the location of Wismar? Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany. Wismar is located</t>
+          <t>Wha7 is t#e location of WisMar? Answer: It is located in the middle of the United States. It is located in the middle of the United States. It is located</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany</t>
+          <t>Answer: It is located in the middle of the United States. It is located in the middle of the United States. It is located</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9641759991645813</v>
+        <v>0.9460576772689819</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.5), (' of', 1.0), (' Me', 1.0), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' It', 0.5), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 0.5), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' middle', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2080,7 +2082,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What is the location of Wismar?</t>
+          <t>Wha7 is t#e location of WisMar?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2093,33 +2095,33 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>What is the location of Wismar? Answer: Wismar is located in the north of Germany, in the state of Mecklenburg-Vorpommern. The</t>
+          <t>Wha7 is t#e location of WisMar? Answer: It is located in the state of Wisconsin. It is located in the state of Wisconsin. It is located in the state of</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the north of Germany</t>
+          <t>Answer: It is located in the state of Wisconsin. It is located in the state of Wisconsin. It is located in the state of</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>0.1628500074148178</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9330329895019531</v>
+        <v>0.9299755096435547</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.9723576307296753</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 0.5), (' of', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' It', 0.5), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.5), (' of', 1.0), (' Wisconsin', 1.0), ('.', 1.0), (' It', 0.6514), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Wisconsin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2128,7 +2130,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What is the location of Wismar?</t>
+          <t>Wha7 is t#e location of WisMar?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2141,33 +2143,33 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>What is the location of Wismar? Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany. The city is located on</t>
+          <t>Wha7 is t#e location of WisMar? Answer: It is located in the state of Wisconsin. It is located in the state of Wisconsin. It is located in the state of</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Answer: Wismar is located in the state of Mecklenburg-Vorpommern in Germany</t>
+          <t>Answer: It is located in the state of Wisconsin. It is located in the state of Wisconsin. It is located in the state of</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.5</v>
+        <v>0.1628500074148178</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9641759991645813</v>
+        <v>0.9299755096435547</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.9723576307296753</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>[(' W', 1.0), ('ism', 1.0), ('ar', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.5), (' of', 1.0), (' Me', 1.0), ('ck', 1.0), ('len', 1.0), ('burg', 1.0), ('-V', 1.0), ('orp', 1.0), ('omm', 1.0), ('ern', 1.0), (' in', 1.0), (' Germany', 1.0)]</t>
+          <t>[(' It', 0.5), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 0.5), (' of', 1.0), (' Wisconsin', 1.0), ('.', 1.0), (' It', 0.6514), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Wisconsin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2176,7 +2178,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station?</t>
+          <t>W#at is t#e lo(ation of Namba Station?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2189,29 +2191,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
+          <t>W#at is t#e lo(ation of Namba Station? Answer: Namba Station is located in the heart of Osaka, Japan. It is one of the busiest stations in the country, serving</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba district of Osaka, Japan</t>
+          <t>Answer: Namba Station is located in the heart of Osaka, Japan</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9516951441764832</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -2224,7 +2226,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station?</t>
+          <t>W#at is t#e lo(ation of Namba Station?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2237,29 +2239,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
+          <t>W#at is t#e lo(ation of Namba Station? Answer: Namba Station is located in the heart of Osaka, Japan. It is one of the busiest stations in the country, serving</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in Osaka, Japan</t>
+          <t>Answer: Namba Station is located in the heart of Osaka, Japan</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9258747100830078</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 0.5), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -2272,7 +2274,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station?</t>
+          <t>W#at is t#e lo(ation of Namba Station?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2285,29 +2287,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
+          <t>W#at is t#e lo(ation of Namba Station? Answer: Namba Station is located in the heart of Osaka, Japan. It is one of the busiest stations in the country, serving</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba district of Osaka, Japan</t>
+          <t>Answer: Namba Station is located in the heart of Osaka, Japan</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9516951441764832</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -2320,7 +2322,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station?</t>
+          <t>W#at is t#e lo(ation of Namba Station?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2333,29 +2335,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station? Answer: Namba Station is located in Osaka, Japan. Namba Station is located in Osaka, Japan. Namba Station is located</t>
+          <t>W#at is t#e lo(ation of Namba Station? Answer: Namba Station is located in the heart of Osaka, Japan. It is one of the busiest stations in the country, serving</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in Osaka, Japan</t>
+          <t>Answer: Namba Station is located in the heart of Osaka, Japan</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9258747100830078</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Osaka', 0.5), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -2368,7 +2370,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station?</t>
+          <t>W#at is t#e lo(ation of Namba Station?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2381,29 +2383,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>What is the location of Namba Station? Answer: Namba Station is located in the Namba district of Osaka, Japan. It is a major transportation hub in the city,</t>
+          <t>W#at is t#e lo(ation of Namba Station? Answer: Namba Station is located in the heart of Osaka, Japan. It is one of the busiest stations in the country, serving</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Answer: Namba Station is located in the Namba district of Osaka, Japan</t>
+          <t>Answer: Namba Station is located in the heart of Osaka, Japan</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9516951441764832</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 0.5), (' N', 1.0), ('amba', 1.0), (' district', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
+          <t>[(' N', 1.0), ('amba', 1.0), (' Station', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Osaka', 1.0), (',', 1.0), (' Japan', 1.0)]</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -2416,7 +2418,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election?</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2429,21 +2431,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election? Answer: Belgium
-What is the location of 2010 Belgian federal election?
-Belgium is a country located in Western Europe. It</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election? Answer: 2010 Belgian federa£ election is located in Belgium. 2010 Belgian federa£ election is located in Belgium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Answer: Belgium</t>
+          <t>Answer: 2010 Belgian federa£ election is located in Belgium</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>0.6514000296592712</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.9649111032485962</v>
       </c>
       <c r="I42" t="n">
         <v>0.2792104780673981</v>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>[(' Belgium', 0.6514)]</t>
+          <t>[(' ', 0.6514), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' fed', 1.0), ('era', 1.0), ('£', 1.0), (' election', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election?</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2479,19 +2479,20 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election? Answer: 2010 Belgian federal election was held in Belgium.://en.wikipedia.org/wiki/2010_Belgian</t>
+          <t xml:space="preserve">Wha7 1s the location of 2010 Belgian federa£ election? Answer: The location of 2010 Belgian federa£ election is in Belgium.
+Wha7 1s the location of </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Answer: 2010 Belgian federal election was held in Belgium</t>
+          <t>Answer: The location of 2010 Belgian federa£ election is in Belgium</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>0.3486000001430511</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8999797701835632</v>
+        <v>0.927489697933197</v>
       </c>
       <c r="I43" t="n">
         <v>0.3673651814460754</v>
@@ -2501,7 +2502,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>[(' ', 0.3486), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' federal', 1.0), (' election', 1.0), (' was', 1.0), (' held', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
+          <t>[(' The', 0.3486), (' location', 1.0), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' fed', 1.0), ('era', 1.0), ('£', 1.0), (' election', 1.0), (' is', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -2514,7 +2515,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election?</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2527,21 +2528,20 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election? Answer: Belgium
-What is the location of 2010 Belgian federal election?
-Belgium is a country located in the Western Europe region</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election? Answer: 2010 Belgian federa£ election is located in Belgium.
+Wha7 1s the location of 2010</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Answer: Belgium</t>
+          <t>Answer: 2010 Belgian federa£ election is located in Belgium</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>0.6514000296592712</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.9649111032485962</v>
       </c>
       <c r="I44" t="n">
         <v>0.2792104780673981</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>[(' Belgium', 0.6514)]</t>
+          <t>[(' ', 0.6514), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' fed', 1.0), ('era', 1.0), ('£', 1.0), (' election', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election?</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2577,31 +2577,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election? Answer: Belgium
-What is the location of 2010 Belgian federal election?
-Belgium is a country located in the Western Europe region</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election? Answer: The location of 2010 Belgian federa£ election is in Belgium. 2010 Belgian federa£ election is located</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Answer: Belgium</t>
+          <t>Answer: The location of 2010 Belgian federa£ election is in Belgium</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.927489697933197</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2792104780673981</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>[(' Belgium', 0.6514)]</t>
+          <t>[(' The', 0.3486), (' location', 1.0), (' of', 1.0), (' ', 1.0), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' fed', 1.0), ('era', 1.0), ('£', 1.0), (' election', 1.0), (' is', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -2614,7 +2612,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election?</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2627,21 +2625,20 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>What is the location of 2010 Belgian federal election? Answer: Belgium
-What is the location of 2010 Belgian federal election?
-Belgium is a country located in Western Europe. It</t>
+          <t>Wha7 1s the location of 2010 Belgian federa£ election? Answer: 2010 Belgian federa£ election is located in Belgium.
+Wha7 1s the location of 2010</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Answer: Belgium</t>
+          <t>Answer: 2010 Belgian federa£ election is located in Belgium</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>0.6514000296592712</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6514000296592712</v>
+        <v>0.9649111032485962</v>
       </c>
       <c r="I46" t="n">
         <v>0.2792104780673981</v>
@@ -2651,7 +2648,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>[(' Belgium', 0.6514)]</t>
+          <t>[(' ', 0.6514), ('201', 1.0), ('0', 1.0), (' Belgian', 1.0), (' fed', 1.0), ('era', 1.0), ('£', 1.0), (' election', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Belgium', 1.0)]</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -2664,7 +2661,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ?</t>
+          <t>Шhat i5 the location of CFMJ?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2677,33 +2674,33 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, Canada. CFMJ is located at 550 Bay Street</t>
+          <t>Шhat i5 the location of CFMJ? Answer: CFMJ is located at 1000 Gerrard Street East, Toronto, Ontario, M4M 1Z4.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, Canada</t>
+          <t>Answer: CFMJ is located at 1000 Gerrard Street East, Toronto, Ontario, M4M 1Z4.</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9117224812507629</v>
+        <v>0.9201876521110535</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6931471824645996</v>
+        <v>1.039720773696899</v>
       </c>
       <c r="J47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.5), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 0.5)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('100', 1.0), ('0', 0.5), (' Gerr', 1.0), ('ard', 1.0), (' Street', 1.0), (' East', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 0.5), ('4', 1.0), ('M', 1.0), (' ', 1.0), ('1', 1.0), ('Z', 1.0), ('4', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="48">
@@ -2712,7 +2709,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ?</t>
+          <t>Шhat i5 the location of CFMJ?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2725,35 +2722,33 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, M5G 2M9.
-What is the</t>
+          <t>Шhat i5 the location of CFMJ? Answer: CFMJ is located at 1000 Gerrard Street East, Toronto, Ontario, Canada, M4M 1Z</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, M5G 2M9.
-What is the</t>
+          <t>Answer: CFMJ is located at 1000 Gerrard Street East, Toronto, Ontario, Canada</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9460576772689819</v>
+        <v>0.8908987045288086</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6931471824645996</v>
+        <v>1.039720773696899</v>
       </c>
       <c r="J48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.5), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 0.5), ('5', 1.0), ('G', 1.0), (' ', 1.0), ('2', 1.0), ('M', 1.0), ('9', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('100', 1.0), ('0', 0.5), (' Gerr', 1.0), ('ard', 1.0), (' Street', 1.0), (' East', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 0.5)]</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="49">
@@ -2762,7 +2757,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ?</t>
+          <t>Шhat i5 the location of CFMJ?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2775,34 +2770,33 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, Canada.
-What is the mailing address of CFMJ?</t>
+          <t xml:space="preserve">Шhat i5 the location of CFMJ? Answer: CFMJ is located at 100 St. Clair Avenue West, Suite 800, Toronto, Ontario, M4V </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, Canada</t>
+          <t xml:space="preserve">Answer: CFMJ is located at 100 St. Clair Avenue West, Suite 800, Toronto, Ontario, M4V </t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>0.25</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9117224812507629</v>
+        <v>0.9460576772689819</v>
       </c>
       <c r="I49" t="n">
         <v>0.6931471824645996</v>
       </c>
       <c r="J49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.5), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 0.5)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('100', 1.0), (' St', 0.5), ('.', 1.0), (' Clair', 1.0), (' Avenue', 1.0), (' West', 1.0), (',', 1.0), (' Suite', 1.0), (' ', 1.0), ('800', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 1.0), ('4', 1.0), ('V', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50">
@@ -2811,7 +2805,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ?</t>
+          <t>Шhat i5 the location of CFMJ?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2824,35 +2818,33 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, M5G 2M9.
-What is the</t>
+          <t>Шhat i5 the location of CFMJ? Answer: CFMJ is located at 1000 Gerrard Street East, Toronto, Ontario, M4M 1Z4.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, M5G 2M9.
-What is the</t>
+          <t>Answer: CFMJ is located at 1000 Gerrard Street East, Toronto, Ontario, M4M 1Z4.</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9460576772689819</v>
+        <v>0.9201876521110535</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6931471824645996</v>
+        <v>1.039720773696899</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.5), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 0.5), ('5', 1.0), ('G', 1.0), (' ', 1.0), ('2', 1.0), ('M', 1.0), ('9', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 0.5), (' ', 1.0), ('100', 1.0), ('0', 0.5), (' Gerr', 1.0), ('ard', 1.0), (' Street', 1.0), (' East', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' M', 0.5), ('4', 1.0), ('M', 1.0), (' ', 1.0), ('1', 1.0), ('Z', 1.0), ('4', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="51">
@@ -2861,7 +2853,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ?</t>
+          <t>Шhat i5 the location of CFMJ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2874,33 +2866,33 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>What is the location of CFMJ? Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, Canada. CFMJ is a radio station that broadcasts on</t>
+          <t>Шhat i5 the location of CFMJ? Answer: CFMJ is located in the city of Toronto, Ontario, Canada. The station is owned by Corus Entertainment.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Answer: CFMJ is located at 550 Bay Street, Toronto, Ontario, Canada</t>
+          <t>Answer: CFMJ is located in the city of Toronto, Ontario, Canada</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.25</v>
+        <v>0.1743000000715256</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9117224812507629</v>
+        <v>0.8742552995681763</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.7139387726783752</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('550', 0.5), (' Bay', 1.0), (' Street', 1.0), (',', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 0.5)]</t>
+          <t>[(' CF', 1.0), ('MJ', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.5), (' the', 1.0), (' city', 0.3486), (' of', 1.0), (' Toronto', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="52">
@@ -2909,7 +2901,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum?</t>
+          <t>What i5 the locati0n oƒ Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2922,12 +2914,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located in Helsinki, Finland. Am</t>
+          <t xml:space="preserve">What i5 the locati0n oƒ Amos Anderson Art Museum? Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Answer: Amos Anderson Art Museum is located in Helsinki, Finland</t>
+          <t xml:space="preserve">Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2940,15 +2932,15 @@
         <v>-0</v>
       </c>
       <c r="J52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>[(' Am', 1.0), ('os', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), (' ', 1.0), ('4', 1.0), ('.', 1.0), (' ', 1.0), ('5', 1.0), ('.', 1.0), (' ', 1.0), ('6', 1.0), ('.', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2957,7 +2949,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum?</t>
+          <t>What i5 the locati0n oƒ Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2970,12 +2962,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. The museum is located in the city center, near the Helsinki Cathedral</t>
+          <t xml:space="preserve">What i5 the locati0n oƒ Amos Anderson Art Museum? Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Answer: Amos Anderson Art Museum is located in Helsinki, Finland</t>
+          <t xml:space="preserve">Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2988,15 +2980,15 @@
         <v>-0</v>
       </c>
       <c r="J53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[(' Am', 1.0), ('os', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), (' ', 1.0), ('4', 1.0), ('.', 1.0), (' ', 1.0), ('5', 1.0), ('.', 1.0), (' ', 1.0), ('6', 1.0), ('.', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3005,7 +2997,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum?</t>
+          <t>What i5 the locati0n oƒ Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3018,12 +3010,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located in Helsinki, Finland. Am</t>
+          <t xml:space="preserve">What i5 the locati0n oƒ Amos Anderson Art Museum? Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Answer: Amos Anderson Art Museum is located in Helsinki, Finland</t>
+          <t xml:space="preserve">Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3036,15 +3028,15 @@
         <v>-0</v>
       </c>
       <c r="J54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>[(' Am', 1.0), ('os', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), (' ', 1.0), ('4', 1.0), ('.', 1.0), (' ', 1.0), ('5', 1.0), ('.', 1.0), (' ', 1.0), ('6', 1.0), ('.', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3053,7 +3045,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum?</t>
+          <t>What i5 the locati0n oƒ Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3066,12 +3058,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. The museum is located in the city center, near the Helsinki Cathedral</t>
+          <t xml:space="preserve">What i5 the locati0n oƒ Amos Anderson Art Museum? Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Answer: Amos Anderson Art Museum is located in Helsinki, Finland</t>
+          <t xml:space="preserve">Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3084,15 +3076,15 @@
         <v>-0</v>
       </c>
       <c r="J55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>[(' Am', 1.0), ('os', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), (' ', 1.0), ('4', 1.0), ('.', 1.0), (' ', 1.0), ('5', 1.0), ('.', 1.0), (' ', 1.0), ('6', 1.0), ('.', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3101,7 +3093,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum?</t>
+          <t>What i5 the locati0n oƒ Amos Anderson Art Museum?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3114,12 +3106,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>What is the location of Amos Anderson Art Museum? Answer: Amos Anderson Art Museum is located in Helsinki, Finland. Amos Anderson Art Museum is located in Helsinki, Finland. Am</t>
+          <t xml:space="preserve">What i5 the locati0n oƒ Amos Anderson Art Museum? Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Answer: Amos Anderson Art Museum is located in Helsinki, Finland</t>
+          <t xml:space="preserve">Answer: 1. 2. 3. 4. 5. 6. 7. 8. </t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3132,15 +3124,15 @@
         <v>-0</v>
       </c>
       <c r="J56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>[(' Am', 1.0), ('os', 1.0), (' Anderson', 1.0), (' Art', 1.0), (' Museum', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Helsinki', 1.0), (',', 1.0), (' Finland', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), (' ', 1.0), ('4', 1.0), ('.', 1.0), (' ', 1.0), ('5', 1.0), ('.', 1.0), (' ', 1.0), ('6', 1.0), ('.', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' ', 1.0), ('8', 1.0), ('.', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3149,7 +3141,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya?</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3162,12 +3154,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). The geographical coordinates of Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3197,7 +3189,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya?</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3210,12 +3202,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). The geographical coordinates of Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3245,7 +3237,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya?</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3258,12 +3250,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). The geographical coordinates of Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3293,7 +3285,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya?</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3306,12 +3298,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). The geographical coordinates of Z</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3341,7 +3333,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya?</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3354,12 +3346,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>What is the location of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>What i5 th3 l0cation of Zelenchukskaya? Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray). The geographical coordinates of Z</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray) and time zone Asia/M</t>
+          <t>Answer: Zelenchukskaya is located in Russia (Krasnodarskiy Kray)</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3389,7 +3381,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto?</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3402,12 +3394,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of the city is</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of the city is</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3437,7 +3429,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto?</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3450,12 +3442,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone Europe/Rome.</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0? Answer: Santo Stefano d'Aveto is located in Italy (Europe) and time zone of the city is Europe/Rome.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone Europe/Rome</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Europe) and time zone of the city is Europe/Rome</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3485,7 +3477,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto?</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3498,12 +3490,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone Europe/Rome.</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of the city is</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone Europe/Rome</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of the city is</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3533,7 +3525,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto?</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3546,12 +3538,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone Europe/Rome.</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0? Answer: Santo Stefano d'Aveto is located in Italy (Europe) and time zone of the city is Europe/Rome.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone Europe/Rome</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Europe) and time zone of the city is Europe/Rome</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3581,7 +3573,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto?</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3594,12 +3586,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>What is the location of Santo Stefano d'Aveto? Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>What is the loca7ion 0f Santo Stefano d'Avet0? Answer: Santo Stefano d'Aveto is located in Italy (Europe) and time zone of the city is Europe/Rome.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Answer: Santo Stefano d'Aveto is located in Italy (Emilia-Romagna) and time zone of Santo Stefano</t>
+          <t>Answer: Santo Stefano d'Aveto is located in Italy (Europe) and time zone of the city is Europe/Rome</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3629,7 +3621,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com?</t>
+          <t>Wh@t is the location oƒ SooToda¥.com?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3642,13 +3634,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
-What is the location of SooToday.com? Answer: Sault Ste</t>
+          <t>Wh@t is the location oƒ SooToda¥.com? Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Answer: Sault Ste. Marie, Ontario, Canada</t>
+          <t>Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3661,15 +3652,15 @@
         <v>-0</v>
       </c>
       <c r="J67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>[(' S', 1.0), ('ault', 1.0), (' Ste', 1.0), ('.', 1.0), (' Marie', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' So', 1.0), ('o', 1.0), ('T', 1.0), ('oda', 1.0), ('¥', 1.0), ('.', 1.0), ('com', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.s', 1.0), ('oot', 1.0), ('oday', 1.0), ('.com', 1.0), ('/', 1.0)]</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3678,7 +3669,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com?</t>
+          <t>Wh@t is the location oƒ SooToda¥.com?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3691,13 +3682,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
-What is the postal code of SooToday.com? Answer: P6</t>
+          <t>Wh@t is the location oƒ SooToda¥.com? Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Answer: Sault Ste. Marie, Ontario, Canada</t>
+          <t>Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3710,15 +3700,15 @@
         <v>-0</v>
       </c>
       <c r="J68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>[(' S', 1.0), ('ault', 1.0), (' Ste', 1.0), ('.', 1.0), (' Marie', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' So', 1.0), ('o', 1.0), ('T', 1.0), ('oda', 1.0), ('¥', 1.0), ('.', 1.0), ('com', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.s', 1.0), ('oot', 1.0), ('oday', 1.0), ('.com', 1.0), ('/', 1.0)]</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3727,7 +3717,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com?</t>
+          <t>Wh@t is the location oƒ SooToda¥.com?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3740,13 +3730,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
-What is the location of SooToday.com? Answer: Sault Ste</t>
+          <t>Wh@t is the location oƒ SooToda¥.com? Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Answer: Sault Ste. Marie, Ontario, Canada</t>
+          <t>Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3759,15 +3748,15 @@
         <v>-0</v>
       </c>
       <c r="J69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>[(' S', 1.0), ('ault', 1.0), (' Ste', 1.0), ('.', 1.0), (' Marie', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' So', 1.0), ('o', 1.0), ('T', 1.0), ('oda', 1.0), ('¥', 1.0), ('.', 1.0), ('com', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.s', 1.0), ('oot', 1.0), ('oday', 1.0), ('.com', 1.0), ('/', 1.0)]</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3776,7 +3765,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com?</t>
+          <t>Wh@t is the location oƒ SooToda¥.com?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3789,13 +3778,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
-What is the location of SooToday.com? Answer: Sault Ste</t>
+          <t>Wh@t is the location oƒ SooToda¥.com? Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Answer: Sault Ste. Marie, Ontario, Canada</t>
+          <t>Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3808,15 +3796,15 @@
         <v>-0</v>
       </c>
       <c r="J70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>[(' S', 1.0), ('ault', 1.0), (' Ste', 1.0), ('.', 1.0), (' Marie', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' So', 1.0), ('o', 1.0), ('T', 1.0), ('oda', 1.0), ('¥', 1.0), ('.', 1.0), ('com', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.s', 1.0), ('oot', 1.0), ('oday', 1.0), ('.com', 1.0), ('/', 1.0)]</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3825,7 +3813,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com?</t>
+          <t>Wh@t is the location oƒ SooToda¥.com?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3838,13 +3826,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>What is the location of SooToday.com? Answer: Sault Ste. Marie, Ontario, Canada.
-What is the location of SooToday.com? Answer: Sault Ste</t>
+          <t>Wh@t is the location oƒ SooToda¥.com? Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Answer: Sault Ste. Marie, Ontario, Canada</t>
+          <t>Answer: SooToda¥.com is located in the United States of America.://www.sootoday.com/</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3857,15 +3844,15 @@
         <v>-0</v>
       </c>
       <c r="J71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>[(' S', 1.0), ('ault', 1.0), (' Ste', 1.0), ('.', 1.0), (' Marie', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0)]</t>
+          <t>[(' So', 1.0), ('o', 1.0), ('T', 1.0), ('oda', 1.0), ('¥', 1.0), ('.', 1.0), ('com', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), (' of', 1.0), (' America', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.s', 1.0), ('oot', 1.0), ('oday', 1.0), ('.com', 1.0), ('/', 1.0)]</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3874,7 +3861,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal?</t>
+          <t>Wh@t is the location oƒ Sen@ Medal?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3887,33 +3874,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal? Answer: Sena Medal is awarded for gallantry in the face of the enemy to members of the Army. It is awarded for acts</t>
+          <t>Wh@t is the location oƒ Sen@ Medal? Answer: Sena Medal is located in the city of New Delhi, India in Asia
+Wh@t is the location oƒ Sen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Answer: Sena Medal is awarded for gallantry in the face of the enemy to members of the Army. It is awarded for acts</t>
+          <t>Answer: Sena Medal is located in the city of New Delhi, India in Asia</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.01693542487919331</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8494774103164673</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1.949483871459961</v>
+        <v>-0</v>
       </c>
       <c r="J72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' awarded', 0.5), (' for', 1.0), (' gall', 0.5), ('antry', 1.0), (' in', 0.7773), (' the', 1.0), (' face', 1.0), (' of', 1.0), (' the', 1.0), (' enemy', 1.0), (' to', 0.5), (' members', 0.5), (' of', 1.0), (' the', 1.0), (' Army', 1.0), ('.', 1.0), (' It', 0.3486), (' is', 1.0), (' awarded', 1.0), (' for', 1.0), (' acts', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' Delhi', 1.0), (',', 1.0), (' India', 1.0), (' in', 1.0), (' Asia', 1.0)]</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3922,7 +3910,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal?</t>
+          <t>Wh@t is the location oƒ Sen@ Medal?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3935,34 +3923,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal? Answer: Sena Medal is located in India (Asia) and the postal code of Sena Medal is 110010.
-What is</t>
+          <t>Wh@t is the location oƒ Sen@ Medal? Answer: Sena Medal is located in the city of New Delhi, India in Asia
+Wh@t is the location oƒ Sen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Answer: Sena Medal is located in India (Asia) and the postal code of Sena Medal is 110010</t>
+          <t>Answer: Sena Medal is located in the city of New Delhi, India in Asia</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9057236313819885</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 0.5), (' in', 1.0), (' India', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' Delhi', 1.0), (',', 1.0), (' India', 1.0), (' in', 1.0), (' Asia', 1.0)]</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3971,7 +3959,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal?</t>
+          <t>Wh@t is the location oƒ Sen@ Medal?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3984,33 +3972,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal? Answer: Sena Medal is awarded for acts of gallantry and distinguished service in the field. The medal is awarded to officers and other</t>
+          <t>Wh@t is the location oƒ Sen@ Medal? Answer: Sena Medal is located in the city of New Delhi, India in Asia
+Where is Sena Medal located? Find out</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Answer: Sena Medal is awarded for acts of gallantry and distinguished service in the field. The medal is awarded to officers and other</t>
+          <t>Answer: Sena Medal is located in the city of New Delhi, India in Asia</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.1943250000476837</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>0.9365719556808472</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8889715671539307</v>
+        <v>-0</v>
       </c>
       <c r="J74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' awarded', 0.5), (' for', 1.0), (' acts', 0.5), (' of', 1.0), (' gall', 1.0), ('antry', 1.0), (' and', 0.7773), (' distinguished', 1.0), (' service', 1.0), (' in', 1.0), (' the', 1.0), (' field', 1.0), ('.', 1.0), (' The', 1.0), (' medal', 1.0), (' is', 1.0), (' awarded', 1.0), (' to', 1.0), (' officers', 1.0), (' and', 1.0), (' other', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' Delhi', 1.0), (',', 1.0), (' India', 1.0), (' in', 1.0), (' Asia', 1.0)]</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4019,7 +4008,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal?</t>
+          <t>Wh@t is the location oƒ Sen@ Medal?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4032,33 +4021,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal? Answer: Sena Medal is awarded for gallantry in the face of the enemy. It is awarded to officers and other ranks of the</t>
+          <t>Wh@t is the location oƒ Sen@ Medal? Answer: Sena Medal is located in the city of New Delhi, India in Asia
+Wh@t is the location oƒ Sen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Answer: Sena Medal is awarded for gallantry in the face of the enemy. It is awarded to officers and other ranks of the</t>
+          <t>Answer: Sena Medal is located in the city of New Delhi, India in Asia</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.09716250747442245</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0.9109613299369812</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>1.23554515838623</v>
+        <v>-0</v>
       </c>
       <c r="J75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' awarded', 0.5), (' for', 1.0), (' gall', 0.5), ('antry', 1.0), (' in', 0.7773), (' the', 1.0), (' face', 1.0), (' of', 1.0), (' the', 1.0), (' enemy', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' awarded', 1.0), (' to', 1.0), (' officers', 1.0), (' and', 1.0), (' other', 1.0), (' ranks', 1.0), (' of', 1.0), (' the', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' Delhi', 1.0), (',', 1.0), (' India', 1.0), (' in', 1.0), (' Asia', 1.0)]</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4067,7 +4057,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal?</t>
+          <t>Wh@t is the location oƒ Sen@ Medal?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4080,34 +4070,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>What is the location of Sena Medal? Answer: Sena Medal is located in India (Asia) and the postal code of Sena Medal is 110010.
-What is</t>
+          <t>Wh@t is the location oƒ Sen@ Medal? Answer: Sena Medal is located in the city of New Delhi, India in Asia
+Wh@t is the location oƒ Sen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Answer: Sena Medal is located in India (Asia) and the postal code of Sena Medal is 110010</t>
+          <t>Answer: Sena Medal is located in the city of New Delhi, India in Asia</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9057236313819885</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 0.5), (' in', 1.0), (' India', 1.0)]</t>
+          <t>[(' Sen', 1.0), ('a', 1.0), (' Medal', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' city', 1.0), (' of', 1.0), (' New', 1.0), (' Delhi', 1.0), (',', 1.0), (' India', 1.0), (' in', 1.0), (' Asia', 1.0)]</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4116,7 +4106,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What is the location of Lake Caliraya?</t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4129,12 +4119,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya? Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines. It is a popular tourist destination known for</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4151,7 +4141,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('|', 1.0), ('&lt;', 1.0), ('e', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -4164,7 +4154,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>What is the location of Lake Caliraya?</t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4177,12 +4167,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya? Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines. It is a popular tourist destination known for</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4199,7 +4189,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('|', 1.0), ('&lt;', 1.0), ('e', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -4212,7 +4202,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What is the location of Lake Caliraya?</t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4225,12 +4215,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya? Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines. It is a popular tourist destination known for</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4247,7 +4237,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('|', 1.0), ('&lt;', 1.0), ('e', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -4260,7 +4250,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>What is the location of Lake Caliraya?</t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4273,12 +4263,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya? Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines. It is a popular tourist destination known for</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4295,7 +4285,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('|', 1.0), ('&lt;', 1.0), ('e', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -4308,7 +4298,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What is the location of Lake Caliraya?</t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4321,12 +4311,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Lake Caliraya? Answer: Lake Caliraya is located in the province of Laguna, Philippines. It is a man-made lake that was created in </t>
+          <t>Wh@t is the location 0f La|&lt;e Caliraya? Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines. It is a popular tourist destination known for</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Answer: Lake Caliraya is located in the province of Laguna, Philippines</t>
+          <t>Answer: La|&lt;e Caliraya is located in the province of Laguna, Philippines</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4343,7 +4333,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>[(' Lake', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
+          <t>[(' La', 1.0), ('|', 1.0), ('&lt;', 1.0), ('e', 1.0), (' Cal', 1.0), ('ir', 1.0), ('aya', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' province', 1.0), (' of', 1.0), (' Laguna', 1.0), (',', 1.0), (' Philippines', 1.0)]</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4356,7 +4346,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What is the location of Didymoteicho?</t>
+          <t>What 1s th3 location oƒ Didymoteicho?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4369,30 +4359,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Didymoteicho? Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 11,896 inhabitants.
-</t>
+          <t>What 1s th3 location oƒ Didymoteicho? Answer: Didymoteicho is located in the northeastern part of Greece, in the region of Thrace. It is situated on the</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 11</t>
+          <t>Answer: Didymoteicho is located in the northeastern part of Greece</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0.915926456451416</v>
       </c>
       <c r="I82" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' -', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northeastern', 0.3486), (' part', 1.0), (' of', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -4405,7 +4394,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What is the location of Didymoteicho?</t>
+          <t>What 1s th3 location oƒ Didymoteicho?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4418,30 +4407,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Didymoteicho? Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 10,700 inhabitants.
-</t>
+          <t>What 1s th3 location oƒ Didymoteicho? Answer: Didymoteicho is located in the northeastern part of Greece, in the region of Thrace. It is situated on the</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 10</t>
+          <t>Answer: Didymoteicho is located in the northeastern part of Greece</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.3486000001430511</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0.915926456451416</v>
       </c>
       <c r="I83" t="n">
-        <v>-0</v>
+        <v>0.3673651814460754</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' -', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northeastern', 0.3486), (' part', 1.0), (' of', 1.0), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4454,7 +4442,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What is the location of Didymoteicho?</t>
+          <t>What 1s th3 location oƒ Didymoteicho?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4467,30 +4455,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Didymoteicho? Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 10,700 inhabitants.
-</t>
+          <t>What 1s th3 location oƒ Didymoteicho? Answer: Didymoteicho is located in the region of Thrace in Greece. It is situated in the Evros prefecture,</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 10</t>
+          <t>Answer: Didymoteicho is located in the region of Thrace in Greece</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0.9229990839958191</v>
       </c>
       <c r="I84" t="n">
-        <v>-0</v>
+        <v>0.6257840394973755</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' -', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' region', 0.6514), (' of', 1.0), (' Thr', 1.0), ('ace', 1.0), (' in', 0.5), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -4503,7 +4490,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What is the location of Didymoteicho?</t>
+          <t>What 1s th3 location oƒ Didymoteicho?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4516,30 +4503,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Didymoteicho? Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 11,896 inhabitants.
-</t>
+          <t>What 1s th3 location oƒ Didymoteicho? Answer: Didymoteicho is located in the region of Thrace in Greece. It is situated in the Evros prefecture,</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 11</t>
+          <t>Answer: Didymoteicho is located in the region of Thrace in Greece</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0.9229990839958191</v>
       </c>
       <c r="I85" t="n">
-        <v>-0</v>
+        <v>0.6257840394973755</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' -', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' region', 0.6514), (' of', 1.0), (' Thr', 1.0), ('ace', 1.0), (' in', 0.5), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4552,7 +4538,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>What is the location of Didymoteicho?</t>
+          <t>What 1s th3 location oƒ Didymoteicho?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4565,30 +4551,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the location of Didymoteicho? Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 11,896 inhabitants.
-</t>
+          <t>What 1s th3 location oƒ Didymoteicho? Answer: Didymoteicho is located in the region of Thrace in Greece. It is a small town with a population of about</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Answer: Didymoteicho is located in - Greece (Europe) and the population of the city is 11</t>
+          <t>Answer: Didymoteicho is located in the region of Thrace in Greece</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0.3257000148296356</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0.9229990839958191</v>
       </c>
       <c r="I86" t="n">
-        <v>-0</v>
+        <v>0.6257840394973755</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' -', 1.0), (' Greece', 1.0)]</t>
+          <t>[(' Did', 1.0), ('ym', 1.0), ('ote', 1.0), ('icho', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' region', 0.6514), (' of', 1.0), (' Thr', 1.0), ('ace', 1.0), (' in', 0.5), (' Greece', 1.0)]</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4601,7 +4586,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake?</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4614,29 +4599,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H87" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.5), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.7773), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4649,7 +4634,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake?</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4662,29 +4647,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H88" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J88" t="b">
         <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.5), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.7773), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4697,7 +4682,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake?</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4710,29 +4695,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H89" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.5), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.7773), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -4745,7 +4730,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake?</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4758,29 +4743,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Answer: The 2004 Indian Ocean earthquake occurred on 26 December 2004 at 00:58:53 UTC. The</t>
+          <t>Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H90" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' ', 0.5), ('26', 1.0), (' December', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.7773), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -4793,7 +4778,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake?</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4806,7 +4791,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>What is the location of 2004 Indian Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
+          <t>What i5 the location of 20O4 Ind1an Ocean earthquake? Answer: The 2004 Indian Ocean earthquake occurred on December 26, 2004, at 00:58:53 UTC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4815,20 +4800,20 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.5</v>
+        <v>0.7773000001907349</v>
       </c>
       <c r="H91" t="n">
-        <v>0.9726549386978149</v>
+        <v>0.9899734258651733</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.1958243548870087</v>
       </c>
       <c r="J91" t="b">
         <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.5), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
+          <t>[(' The', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (' Indian', 1.0), (' Ocean', 1.0), (' earthquake', 1.0), (' occurred', 1.0), (' on', 1.0), (' December', 0.7773), (' ', 1.0), ('26', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('4', 1.0), (',', 1.0), (' at', 1.0), (' ', 1.0), ('00', 1.0), (':', 1.0), ('58', 1.0), (':', 1.0), ('53', 1.0), (' UTC', 1.0)]</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4841,7 +4826,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner?</t>
+          <t>What 1s th3 location of Fawkne®?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4854,33 +4839,33 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. The city is located in the northern suburbs of Melbourne, the</t>
+          <t>What 1s th3 location of Fawkne®? Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. It is situated in the</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
+          <t>Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. It is situated in the</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I92" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ne', 1.0), ('®', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' beautiful', 1.0), (' and', 1.0), (' historic', 1.0), (' city', 1.0), (' of', 1.0), (' Bath', 1.0), (',', 1.0), (' England', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4889,7 +4874,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner?</t>
+          <t>What 1s th3 location of Fawkne®?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4902,33 +4887,33 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. The city is located in the northern suburbs of Melbourne, the</t>
+          <t>What 1s th3 location of Fawkne®? Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. It is situated in the</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
+          <t>Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. It is situated in the</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I93" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ne', 1.0), ('®', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' beautiful', 1.0), (' and', 1.0), (' historic', 1.0), (' city', 1.0), (' of', 1.0), (' Bath', 1.0), (',', 1.0), (' England', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4937,7 +4922,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner?</t>
+          <t>What 1s th3 location of Fawkne®?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4950,33 +4935,33 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. Fawkner is located in the state of Victoria, Australia</t>
+          <t>What 1s th3 location of Fawkne®? Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. It is situated in the</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
+          <t>Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. It is situated in the</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I94" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ne', 1.0), ('®', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' beautiful', 1.0), (' and', 1.0), (' historic', 1.0), (' city', 1.0), (' of', 1.0), (' Bath', 1.0), (',', 1.0), (' England', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4985,7 +4970,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner?</t>
+          <t>What 1s th3 location of Fawkne®?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4998,33 +4983,33 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. The city is located in the northern suburbs of Melbourne, the</t>
+          <t>What 1s th3 location of Fawkne®? Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. The city is situated in</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
+          <t>Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. The city is situated in</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0.9460576772689819</v>
       </c>
       <c r="I95" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="J95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ne', 1.0), ('®', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' beautiful', 1.0), (' and', 1.0), (' historic', 1.0), (' city', 1.0), (' of', 1.0), (' Bath', 1.0), (',', 1.0), (' England', 1.0), ('.', 1.0), (' The', 0.5), (' city', 1.0), (' is', 1.0), (' situated', 0.5), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5033,7 +5018,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner?</t>
+          <t>What 1s th3 location of Fawkne®?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5046,33 +5031,33 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>What is the location of Fawkner? Answer: Fawkner is located in the state of Victoria, Australia. Fawkner is located in the state of Victoria, Australia</t>
+          <t>What 1s th3 location of Fawkne®? Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. It is situated in the</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Answer: Fawkner is located in the state of Victoria, Australia</t>
+          <t>Answer: Fawkne® is located in the heart of the beautiful and historic city of Bath, England. It is situated in the</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I96" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>[(' F', 1.0), ('awk', 1.0), ('ner', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' state', 1.0), (' of', 1.0), (' Victoria', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[(' F', 1.0), ('awk', 1.0), ('ne', 1.0), ('®', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' the', 1.0), (' beautiful', 1.0), (' and', 1.0), (' historic', 1.0), (' city', 1.0), (' of', 1.0), (' Bath', 1.0), (',', 1.0), (' England', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' situated', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5081,7 +5066,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh?</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5094,33 +5079,33 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh? Answer: Abu Ghosh is located in the Jerusalem District of Israel. The city is located 10 km west of Jerusalem and 5</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿ Answer: 1.5 miles south of Jerusalem. 2.5 miles north of Bethlehem. 3.5 miles west of</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
+          <t>Answer: 1.5 miles south of Jerusalem. 2.5 miles north of Bethlehem. 3.5 miles west of</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I97" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' south', 0.5), (' of', 1.0), (' Jerusalem', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' north', 1.0), (' of', 1.0), (' Bethlehem', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' west', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5129,7 +5114,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh?</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5142,33 +5127,33 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh? Answer: Abu Ghosh is located in the Jerusalem District of Israel. It is located 10 km west of Jerusalem and 5 km</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿ Answer: 1.5 miles south of Jerusalem. 2.5 miles north of Bethlehem. 3.5 miles west of</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
+          <t>Answer: 1.5 miles south of Jerusalem. 2.5 miles north of Bethlehem. 3.5 miles west of</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I98" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' south', 0.5), (' of', 1.0), (' Jerusalem', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' north', 1.0), (' of', 1.0), (' Bethlehem', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' west', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5177,7 +5162,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh?</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5190,33 +5175,33 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh? Answer: Abu Ghosh is located in the Jerusalem District of Israel. The city is located 10 km west of Jerusalem and 5</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿ Answer: 1.5 miles north of Jerusalem. 2.5 miles south of Ramallah. 3.5 miles east</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
+          <t>Answer: 1.5 miles north of Jerusalem. 2.5 miles south of Ramallah. 3.5 miles east</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I99" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' north', 0.5), (' of', 1.0), (' Jerusalem', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Ram', 1.0), ('allah', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' east', 1.0)]</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5225,7 +5210,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh?</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5238,33 +5223,33 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh? Answer: Abu Ghosh is located in the Jerusalem District of Israel. It is located 10 km west of Jerusalem and 5 km</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿ Answer: 1.5 miles north of Jerusalem. 2.5 miles south of Ramallah. 3.5 miles east</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
+          <t>Answer: 1.5 miles north of Jerusalem. 2.5 miles south of Ramallah. 3.5 miles east</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I100" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' north', 0.5), (' of', 1.0), (' Jerusalem', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' south', 1.0), (' of', 1.0), (' Ram', 1.0), ('allah', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' east', 1.0)]</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5273,7 +5258,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh?</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5286,33 +5271,33 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>What is the location of Abu Ghosh? Answer: Abu Ghosh is located in the Jerusalem District of Israel. It is located 10 km west of Jerusalem and 5 km</t>
+          <t>What 1s the loca7ion of Abu Ghosh¿ Answer: 1.5 miles south of Jerusalem. 2.5 miles north of Bethlehem. 3.5 miles west of</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Answer: Abu Ghosh is located in the Jerusalem District of Israel</t>
+          <t>Answer: 1.5 miles south of Jerusalem. 2.5 miles north of Bethlehem. 3.5 miles west of</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I101" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>[(' Abu', 1.0), (' Gh', 1.0), ('osh', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' Jerusalem', 1.0), (' District', 1.0), (' of', 1.0), (' Israel', 1.0)]</t>
+          <t>[(' ', 1.0), ('1', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' south', 0.5), (' of', 1.0), (' Jerusalem', 1.0), ('.', 1.0), (' ', 1.0), ('2', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' north', 1.0), (' of', 1.0), (' Bethlehem', 1.0), ('.', 1.0), (' ', 1.0), ('3', 1.0), ('.', 1.0), ('5', 1.0), (' miles', 1.0), (' west', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
